--- a/public/assets/template/template001.xlsx
+++ b/public/assets/template/template001.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anisa\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96926E44-4B3C-414F-8D14-AEF91DF8626C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F46FC6-A223-432B-8860-421BF7989C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F10FAC9E-B391-42D5-91C2-9705144F9B3C}"/>
   </bookViews>
@@ -169,7 +169,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -184,25 +184,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-4.9989318521683403E-2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -356,21 +338,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -434,6 +407,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -751,156 +729,173 @@
   <dimension ref="A1:T40"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.44140625" customWidth="1"/>
-    <col min="2" max="2" width="29" customWidth="1"/>
-    <col min="3" max="3" width="29.109375" customWidth="1"/>
-    <col min="4" max="5" width="12.88671875" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" customWidth="1"/>
-    <col min="7" max="7" width="18.44140625" customWidth="1"/>
-    <col min="8" max="8" width="20.5546875" customWidth="1"/>
-    <col min="9" max="9" width="19.77734375" customWidth="1"/>
-    <col min="10" max="10" width="20.21875" customWidth="1"/>
-    <col min="11" max="12" width="20.33203125" customWidth="1"/>
-    <col min="13" max="13" width="23.21875" customWidth="1"/>
-    <col min="14" max="14" width="23.88671875" customWidth="1"/>
-    <col min="15" max="15" width="29.44140625" customWidth="1"/>
-    <col min="16" max="16" width="14.88671875" customWidth="1"/>
+    <col min="1" max="1" width="24.44140625" style="26" customWidth="1"/>
+    <col min="2" max="2" width="29" style="26" customWidth="1"/>
+    <col min="3" max="3" width="29.109375" style="26" customWidth="1"/>
+    <col min="4" max="5" width="12.88671875" style="26" customWidth="1"/>
+    <col min="6" max="6" width="13.21875" style="26" customWidth="1"/>
+    <col min="7" max="7" width="18.44140625" style="26" customWidth="1"/>
+    <col min="8" max="8" width="20.5546875" style="26" customWidth="1"/>
+    <col min="9" max="9" width="19.77734375" style="26" customWidth="1"/>
+    <col min="10" max="10" width="20.21875" style="26" customWidth="1"/>
+    <col min="11" max="11" width="20.33203125" style="26" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" style="27" customWidth="1"/>
+    <col min="13" max="13" width="23.21875" style="27" customWidth="1"/>
+    <col min="14" max="14" width="23.88671875" style="27" customWidth="1"/>
+    <col min="15" max="15" width="29.44140625" style="27" customWidth="1"/>
+    <col min="16" max="16" width="14.88671875" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="21"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="24"/>
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="21"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="23"/>
-      <c r="H3" s="23"/>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="24"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="21"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="23"/>
-      <c r="H4" s="23"/>
-      <c r="I4" s="23"/>
-      <c r="J4" s="23"/>
-      <c r="K4" s="23"/>
-      <c r="L4" s="23"/>
-      <c r="M4" s="23"/>
-      <c r="N4" s="23"/>
-      <c r="O4" s="23"/>
-      <c r="P4" s="24"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="21"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="24"/>
+      <c r="A5" s="19"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="21"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
-      <c r="D6" s="23"/>
-      <c r="E6" s="23"/>
-      <c r="F6" s="23"/>
-      <c r="G6" s="23"/>
-      <c r="H6" s="23"/>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="24"/>
+      <c r="A6" s="19"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="21"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="26"/>
-      <c r="G7" s="26"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
-      <c r="P7" s="27"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
+      <c r="O7" s="23"/>
+      <c r="P7" s="24"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="R8" s="16" t="s">
+      <c r="A8"/>
+      <c r="B8"/>
+      <c r="C8"/>
+      <c r="D8"/>
+      <c r="E8"/>
+      <c r="F8"/>
+      <c r="G8"/>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8"/>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+      <c r="P8"/>
+      <c r="R8" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="S8" s="17"/>
-      <c r="T8" s="18"/>
+      <c r="S8" s="14"/>
+      <c r="T8" s="15"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -951,587 +946,587 @@
       <c r="P9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R9" s="7" t="s">
+      <c r="R9" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="S9" s="8"/>
-      <c r="T9" s="9"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="6"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="3"/>
-      <c r="O10" s="5"/>
-      <c r="P10" s="5"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="11"/>
-      <c r="T10" s="12"/>
+      <c r="A10" s="25"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="9"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="2"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="3"/>
-      <c r="O11" s="5"/>
-      <c r="P11" s="5"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="11"/>
-      <c r="T11" s="12"/>
+      <c r="A11" s="25"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="9"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="3"/>
-      <c r="O12" s="5"/>
-      <c r="P12" s="5"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="12"/>
+      <c r="A12" s="25"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="9"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="5"/>
-      <c r="P13" s="5"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="11"/>
-      <c r="T13" s="12"/>
+      <c r="A13" s="25"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="9"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="11"/>
-      <c r="T14" s="12"/>
+      <c r="A14" s="25"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="9"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="3"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="3"/>
-      <c r="O15" s="5"/>
-      <c r="P15" s="5"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="14"/>
-      <c r="T15" s="15"/>
+      <c r="A15" s="25"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="12"/>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="5"/>
-      <c r="P16" s="5"/>
+      <c r="A16" s="25"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A17" s="2"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="3"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="3"/>
-      <c r="O17" s="5"/>
-      <c r="P17" s="5"/>
+      <c r="A17" s="25"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="5"/>
-      <c r="P18" s="5"/>
+      <c r="A18" s="25"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="3"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
+      <c r="A19" s="25"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="6"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
+      <c r="A20" s="25"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="3"/>
-      <c r="L21" s="6"/>
-      <c r="M21" s="6"/>
-      <c r="N21" s="3"/>
-      <c r="O21" s="5"/>
-      <c r="P21" s="5"/>
+      <c r="A21" s="25"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="3"/>
-      <c r="O22" s="5"/>
-      <c r="P22" s="5"/>
+      <c r="A22" s="25"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A23" s="2"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="3"/>
-      <c r="O23" s="5"/>
-      <c r="P23" s="5"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="3"/>
-      <c r="O24" s="5"/>
-      <c r="P24" s="5"/>
+      <c r="A24" s="25"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A25" s="2"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="6"/>
-      <c r="M25" s="6"/>
-      <c r="N25" s="3"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
+      <c r="A25" s="25"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="3"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="3"/>
-      <c r="O26" s="5"/>
-      <c r="P26" s="5"/>
+      <c r="A26" s="25"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A27" s="2"/>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="3"/>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A28" s="2"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="3"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="3"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="3"/>
-      <c r="O28" s="5"/>
-      <c r="P28" s="5"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A29" s="2"/>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="4"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="3"/>
-      <c r="O29" s="5"/>
-      <c r="P29" s="5"/>
+      <c r="A29" s="25"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A30" s="2"/>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="4"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="3"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="5"/>
-      <c r="P30" s="5"/>
+      <c r="A30" s="25"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="3"/>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A31" s="2"/>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="3"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="5"/>
-      <c r="P31" s="5"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="25"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A32" s="2"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="6"/>
-      <c r="M32" s="6"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="5"/>
-      <c r="P32" s="5"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="25"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A33" s="2"/>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="G33" s="3"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="3"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="3"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
+      <c r="A33" s="25"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A34" s="2"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="6"/>
-      <c r="M34" s="6"/>
-      <c r="N34" s="3"/>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
+      <c r="A34" s="25"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="25"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A35" s="2"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="G35" s="3"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="3"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="3"/>
-      <c r="O35" s="5"/>
-      <c r="P35" s="5"/>
+      <c r="A35" s="25"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="25"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="6"/>
-      <c r="M36" s="6"/>
-      <c r="N36" s="3"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
+      <c r="A36" s="25"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="25"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A37" s="2"/>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="3"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="3"/>
-      <c r="O37" s="5"/>
-      <c r="P37" s="5"/>
+      <c r="A37" s="25"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="25"/>
+      <c r="M37" s="25"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="25"/>
+      <c r="P37" s="25"/>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A38" s="2"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="4"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="6"/>
-      <c r="M38" s="6"/>
-      <c r="N38" s="3"/>
-      <c r="O38" s="5"/>
-      <c r="P38" s="5"/>
+      <c r="A38" s="25"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="25"/>
+      <c r="M38" s="25"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="25"/>
+      <c r="P38" s="25"/>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A39" s="2"/>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="4"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="3"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="3"/>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
+      <c r="A39" s="25"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="3"/>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="25"/>
+      <c r="M39" s="25"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="25"/>
+      <c r="P39" s="25"/>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A40" s="2"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="4"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="6"/>
-      <c r="N40" s="3"/>
-      <c r="O40" s="5"/>
-      <c r="P40" s="5"/>
+      <c r="A40" s="25"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="3"/>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="25"/>
+      <c r="M40" s="25"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="25"/>
+      <c r="P40" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
